--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/182.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/182.xlsx
@@ -426,13 +426,13 @@
         <v>5.470512062634922</v>
       </c>
       <c r="E2">
-        <v>-14.19709866935673</v>
+        <v>-12.02375719580351</v>
       </c>
       <c r="F2">
-        <v>-1.932303794898816</v>
+        <v>-1.904097884833493</v>
       </c>
       <c r="G2">
-        <v>-8.035059334488825</v>
+        <v>-7.449019942035961</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.049439980749748</v>
       </c>
       <c r="E3">
-        <v>-13.33988118207477</v>
+        <v>-12.77258112923788</v>
       </c>
       <c r="F3">
-        <v>-2.371628446973534</v>
+        <v>-1.917498384308581</v>
       </c>
       <c r="G3">
-        <v>-8.568659685599632</v>
+        <v>-7.810031622547944</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.547380899514285</v>
       </c>
       <c r="E4">
-        <v>-14.15159656252766</v>
+        <v>-12.01177485357922</v>
       </c>
       <c r="F4">
-        <v>-2.339837362788895</v>
+        <v>-1.897457691732652</v>
       </c>
       <c r="G4">
-        <v>-7.859957959825693</v>
+        <v>-6.596723303496133</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.028732571073623</v>
       </c>
       <c r="E5">
-        <v>-16.31127562999974</v>
+        <v>-13.44889513686142</v>
       </c>
       <c r="F5">
-        <v>-2.463144820900018</v>
+        <v>-2.063920606427422</v>
       </c>
       <c r="G5">
-        <v>-7.285429334212875</v>
+        <v>-6.113913342048823</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.518297177537633</v>
       </c>
       <c r="E6">
-        <v>-15.07809517365297</v>
+        <v>-13.99987909784868</v>
       </c>
       <c r="F6">
-        <v>-2.694865691219929</v>
+        <v>-1.781810146995216</v>
       </c>
       <c r="G6">
-        <v>-7.822012486854566</v>
+        <v>-6.594187425613051</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.051291007730873</v>
       </c>
       <c r="E7">
-        <v>-15.24469773239516</v>
+        <v>-14.90609467389363</v>
       </c>
       <c r="F7">
-        <v>-2.721896976308083</v>
+        <v>-1.518118436764258</v>
       </c>
       <c r="G7">
-        <v>-7.271932240049266</v>
+        <v>-5.623058754941084</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>2.660333445430316</v>
       </c>
       <c r="E8">
-        <v>-16.95072333072684</v>
+        <v>-14.4242605110035</v>
       </c>
       <c r="F8">
-        <v>-2.562355899631107</v>
+        <v>-2.102302181668734</v>
       </c>
       <c r="G8">
-        <v>-6.991141699044902</v>
+        <v>-5.964041634940477</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.377527504575839</v>
       </c>
       <c r="E9">
-        <v>-16.90689675928061</v>
+        <v>-15.59315475033738</v>
       </c>
       <c r="F9">
-        <v>-2.757990600782863</v>
+        <v>-2.395979963513631</v>
       </c>
       <c r="G9">
-        <v>-7.206307295824294</v>
+        <v>-4.886045243715297</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.214785816375687</v>
       </c>
       <c r="E10">
-        <v>-16.13604179979893</v>
+        <v>-16.30444669119617</v>
       </c>
       <c r="F10">
-        <v>-2.847812963370622</v>
+        <v>-2.436838357289314</v>
       </c>
       <c r="G10">
-        <v>-6.526351036967845</v>
+        <v>-4.862553612568628</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.18454373271152</v>
       </c>
       <c r="E11">
-        <v>-17.49899926425751</v>
+        <v>-16.72202633639147</v>
       </c>
       <c r="F11">
-        <v>-3.114394019102545</v>
+        <v>-1.916520082405875</v>
       </c>
       <c r="G11">
-        <v>-5.046626565643185</v>
+        <v>-4.546691152121225</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.280904203142708</v>
       </c>
       <c r="E12">
-        <v>-18.58906635653987</v>
+        <v>-16.68400526862307</v>
       </c>
       <c r="F12">
-        <v>-2.372940580939569</v>
+        <v>-2.393965373990023</v>
       </c>
       <c r="G12">
-        <v>-5.380773169103983</v>
+        <v>-4.123984144939383</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.479577620741193</v>
       </c>
       <c r="E13">
-        <v>-18.63523414904807</v>
+        <v>-17.61737810329202</v>
       </c>
       <c r="F13">
-        <v>-2.756981649286253</v>
+        <v>-2.045950003991089</v>
       </c>
       <c r="G13">
-        <v>-3.921398621209223</v>
+        <v>-3.431219385391495</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.759034536549462</v>
       </c>
       <c r="E14">
-        <v>-20.41602485324639</v>
+        <v>-18.02627213534061</v>
       </c>
       <c r="F14">
-        <v>-3.256136793762971</v>
+        <v>-1.869366924736318</v>
       </c>
       <c r="G14">
-        <v>-4.476616834691472</v>
+        <v>-3.481725068138616</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.08763645280723</v>
       </c>
       <c r="E15">
-        <v>-20.47774795397094</v>
+        <v>-18.81623725513466</v>
       </c>
       <c r="F15">
-        <v>-2.601800270250211</v>
+        <v>-2.181267132707999</v>
       </c>
       <c r="G15">
-        <v>-4.715254199344296</v>
+        <v>-2.667234859657265</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.429096837415547</v>
       </c>
       <c r="E16">
-        <v>-21.33146945931897</v>
+        <v>-19.63866700508969</v>
       </c>
       <c r="F16">
-        <v>-2.524618794229172</v>
+        <v>-1.766505230861093</v>
       </c>
       <c r="G16">
-        <v>-3.79449547905234</v>
+        <v>-1.840157957035605</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.758405827677233</v>
       </c>
       <c r="E17">
-        <v>-21.17907725201285</v>
+        <v>-20.42927516819283</v>
       </c>
       <c r="F17">
-        <v>-2.505828936431471</v>
+        <v>-1.792583065068624</v>
       </c>
       <c r="G17">
-        <v>-2.55792395649607</v>
+        <v>-1.757427424009218</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.048761483399315</v>
       </c>
       <c r="E18">
-        <v>-21.8937655483774</v>
+        <v>-21.80153864673718</v>
       </c>
       <c r="F18">
-        <v>-1.987944404977457</v>
+        <v>-1.819480154637524</v>
       </c>
       <c r="G18">
-        <v>-1.785348565087432</v>
+        <v>-1.802851419353558</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.275833434602347</v>
       </c>
       <c r="E19">
-        <v>-22.47432044463474</v>
+        <v>-20.79477736229992</v>
       </c>
       <c r="F19">
-        <v>-2.085265149295356</v>
+        <v>-1.580810110175527</v>
       </c>
       <c r="G19">
-        <v>-2.546820386757354</v>
+        <v>-1.313959985750607</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.425011490449789</v>
       </c>
       <c r="E20">
-        <v>-23.76217769615012</v>
+        <v>-22.40957685174708</v>
       </c>
       <c r="F20">
-        <v>-2.273240765440828</v>
+        <v>-1.078594976512868</v>
       </c>
       <c r="G20">
-        <v>-2.092358626762824</v>
+        <v>-1.421546094685842</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.481907213534029</v>
       </c>
       <c r="E21">
-        <v>-23.3655422432403</v>
+        <v>-22.39271281454252</v>
       </c>
       <c r="F21">
-        <v>-1.906458731931472</v>
+        <v>-1.109994242915984</v>
       </c>
       <c r="G21">
-        <v>-1.632517230266977</v>
+        <v>-1.46838700352099</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.437643635683497</v>
       </c>
       <c r="E22">
-        <v>-23.59660310100767</v>
+        <v>-23.71602348906395</v>
       </c>
       <c r="F22">
-        <v>-1.694862219295172</v>
+        <v>-0.8124256193801369</v>
       </c>
       <c r="G22">
-        <v>-1.884340497802719</v>
+        <v>-1.297152346047727</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.290925228350067</v>
       </c>
       <c r="E23">
-        <v>-23.48892504605329</v>
+        <v>-22.92972643321611</v>
       </c>
       <c r="F23">
-        <v>-1.671212329945246</v>
+        <v>-0.6432464879715882</v>
       </c>
       <c r="G23">
-        <v>-1.734316505599566</v>
+        <v>-0.03194791512230087</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.043475712119274</v>
       </c>
       <c r="E24">
-        <v>-24.85865257915334</v>
+        <v>-23.16596333677425</v>
       </c>
       <c r="F24">
-        <v>-1.173533336180317</v>
+        <v>-0.5181870328035441</v>
       </c>
       <c r="G24">
-        <v>-1.377121884094362</v>
+        <v>-1.012985048593307</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.704818174245707</v>
       </c>
       <c r="E25">
-        <v>-25.84413003575455</v>
+        <v>-24.54110239631347</v>
       </c>
       <c r="F25">
-        <v>-1.434131922529222</v>
+        <v>-0.6281470069533589</v>
       </c>
       <c r="G25">
-        <v>-2.291219786761304</v>
+        <v>-0.755153140903788</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.290084505760011</v>
       </c>
       <c r="E26">
-        <v>-26.74204039046943</v>
+        <v>-24.59884043991127</v>
       </c>
       <c r="F26">
-        <v>-1.238732477719861</v>
+        <v>-0.5527034457433939</v>
       </c>
       <c r="G26">
-        <v>-1.785209522174782</v>
+        <v>-1.698493092319113</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.816391826360154</v>
       </c>
       <c r="E27">
-        <v>-24.9800111540849</v>
+        <v>-24.12617190841266</v>
       </c>
       <c r="F27">
-        <v>-1.560767760864793</v>
+        <v>-0.3659504998844538</v>
       </c>
       <c r="G27">
-        <v>-3.51936597092013</v>
+        <v>-1.267781186023313</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.307346569578291</v>
       </c>
       <c r="E28">
-        <v>-24.97926395587363</v>
+        <v>-23.18890458609711</v>
       </c>
       <c r="F28">
-        <v>-1.218488835130246</v>
+        <v>-0.8083194021644597</v>
       </c>
       <c r="G28">
-        <v>-2.287101468110451</v>
+        <v>-1.778038880536721</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.786954909971974</v>
       </c>
       <c r="E29">
-        <v>-24.41219938368513</v>
+        <v>-23.39017261336802</v>
       </c>
       <c r="F29">
-        <v>-1.233347261234261</v>
+        <v>-0.3689566451892132</v>
       </c>
       <c r="G29">
-        <v>-1.516816974214989</v>
+        <v>-1.744890388051998</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.276261165978569</v>
       </c>
       <c r="E30">
-        <v>-26.24150362992762</v>
+        <v>-22.82417676104533</v>
       </c>
       <c r="F30">
-        <v>-0.810152579226855</v>
+        <v>-0.8756913514015463</v>
       </c>
       <c r="G30">
-        <v>-2.3345746911436</v>
+        <v>-2.179422663900117</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7995229719833506</v>
       </c>
       <c r="E31">
-        <v>-24.56215980044914</v>
+        <v>-22.93193180005785</v>
       </c>
       <c r="F31">
-        <v>-0.5469794269900493</v>
+        <v>-0.3617631026633022</v>
       </c>
       <c r="G31">
-        <v>-2.880006932011764</v>
+        <v>-2.245852070691132</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.376214153830962</v>
       </c>
       <c r="E32">
-        <v>-24.99881337816474</v>
+        <v>-23.06014195616301</v>
       </c>
       <c r="F32">
-        <v>-1.113725209698193</v>
+        <v>-0.07605504360073877</v>
       </c>
       <c r="G32">
-        <v>-3.280748469540541</v>
+        <v>-1.741480526146549</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.01917160022371589</v>
       </c>
       <c r="E33">
-        <v>-23.30064015376237</v>
+        <v>-23.10701619061641</v>
       </c>
       <c r="F33">
-        <v>-0.8703707475733651</v>
+        <v>-0.2759533517747043</v>
       </c>
       <c r="G33">
-        <v>-1.993403110048469</v>
+        <v>-2.259938441960731</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.2577394591362925</v>
       </c>
       <c r="E34">
-        <v>-23.38978316460336</v>
+        <v>-22.08800991246241</v>
       </c>
       <c r="F34">
-        <v>-0.9701434594035515</v>
+        <v>-0.6483608283164723</v>
       </c>
       <c r="G34">
-        <v>-2.214915022626643</v>
+        <v>-2.19680633852683</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4485823795483173</v>
       </c>
       <c r="E35">
-        <v>-23.21300512476593</v>
+        <v>-21.66074838983871</v>
       </c>
       <c r="F35">
-        <v>-0.4946282638679261</v>
+        <v>-0.1346173055090526</v>
       </c>
       <c r="G35">
-        <v>-3.641035140579424</v>
+        <v>-1.788152597159194</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5549071975720744</v>
       </c>
       <c r="E36">
-        <v>-23.18397760637676</v>
+        <v>-21.1219596093541</v>
       </c>
       <c r="F36">
-        <v>-0.7990259482724521</v>
+        <v>-0.2226222300150693</v>
       </c>
       <c r="G36">
-        <v>-2.896109425514779</v>
+        <v>-2.70564049845835</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5773154488985374</v>
       </c>
       <c r="E37">
-        <v>-22.33789110820566</v>
+        <v>-21.85107562390709</v>
       </c>
       <c r="F37">
-        <v>-0.8341023375765944</v>
+        <v>-0.1294159865868745</v>
       </c>
       <c r="G37">
-        <v>-3.863368068451338</v>
+        <v>-2.239538860347742</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5241370939990058</v>
       </c>
       <c r="E38">
-        <v>-21.96037034408221</v>
+        <v>-20.54307572000559</v>
       </c>
       <c r="F38">
-        <v>-0.1546944462507042</v>
+        <v>0.08151120518796361</v>
       </c>
       <c r="G38">
-        <v>-2.888776567145293</v>
+        <v>-2.147763916908066</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4093856487865444</v>
       </c>
       <c r="E39">
-        <v>-20.89264221407969</v>
+        <v>-19.66279471460256</v>
       </c>
       <c r="F39">
-        <v>-0.6441759161975293</v>
+        <v>0.2622974206445389</v>
       </c>
       <c r="G39">
-        <v>-3.796034882728101</v>
+        <v>-1.434394321923754</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2457010590644255</v>
       </c>
       <c r="E40">
-        <v>-21.28517034106455</v>
+        <v>-19.77909045559354</v>
       </c>
       <c r="F40">
-        <v>-1.345603469824636</v>
+        <v>-0.1791652476968044</v>
       </c>
       <c r="G40">
-        <v>-3.578611493890927</v>
+        <v>-2.197935234555721</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.04986527319440534</v>
       </c>
       <c r="E41">
-        <v>-19.66132748902408</v>
+        <v>-19.10223303108908</v>
       </c>
       <c r="F41">
-        <v>-0.3350954708649778</v>
+        <v>0.002787309062912584</v>
       </c>
       <c r="G41">
-        <v>-2.962598422125502</v>
+        <v>-2.130592117195867</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1603394425986664</v>
       </c>
       <c r="E42">
-        <v>-21.32842632478582</v>
+        <v>-17.94883070133544</v>
       </c>
       <c r="F42">
-        <v>-0.9884785434971158</v>
+        <v>-0.1541700896847321</v>
       </c>
       <c r="G42">
-        <v>-2.9035548424326</v>
+        <v>-2.426995190963434</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.370516973716253</v>
       </c>
       <c r="E43">
-        <v>-19.78298947171415</v>
+        <v>-18.56609793637297</v>
       </c>
       <c r="F43">
-        <v>-0.659753365207174</v>
+        <v>0.09458367117154259</v>
       </c>
       <c r="G43">
-        <v>-3.61634509194754</v>
+        <v>-2.879027010532139</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5678454235237101</v>
       </c>
       <c r="E44">
-        <v>-19.64355775701798</v>
+        <v>-18.06705104377968</v>
       </c>
       <c r="F44">
-        <v>-0.6990552566329965</v>
+        <v>0.04427194859511183</v>
       </c>
       <c r="G44">
-        <v>-3.197226716130268</v>
+        <v>-1.861282548121695</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.7417722456037382</v>
       </c>
       <c r="E45">
-        <v>-18.42023578858591</v>
+        <v>-17.01170376171413</v>
       </c>
       <c r="F45">
-        <v>-0.6522177069439069</v>
+        <v>0.02959244985010179</v>
       </c>
       <c r="G45">
-        <v>-2.957238648897421</v>
+        <v>-2.843531341260074</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.8848766975453717</v>
       </c>
       <c r="E46">
-        <v>-17.3360466555655</v>
+        <v>-16.14892983682476</v>
       </c>
       <c r="F46">
-        <v>-0.4953323761603057</v>
+        <v>-0.06797017774941559</v>
       </c>
       <c r="G46">
-        <v>-3.480440576469379</v>
+        <v>-1.72489800354034</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.9918063563321975</v>
       </c>
       <c r="E47">
-        <v>-16.1045598484976</v>
+        <v>-16.8576541329212</v>
       </c>
       <c r="F47">
-        <v>-0.666111913391063</v>
+        <v>-0.3716215031240191</v>
       </c>
       <c r="G47">
-        <v>-3.034861010156713</v>
+        <v>-2.704084542054893</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.058789400062097</v>
       </c>
       <c r="E48">
-        <v>-16.20162768885202</v>
+        <v>-15.98995322831148</v>
       </c>
       <c r="F48">
-        <v>-0.2639279421882638</v>
+        <v>-0.2052000067993901</v>
       </c>
       <c r="G48">
-        <v>-4.2666289311355</v>
+        <v>-2.638264275643103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.084074082032559</v>
       </c>
       <c r="E49">
-        <v>-17.17904446171957</v>
+        <v>-15.6958922401494</v>
       </c>
       <c r="F49">
-        <v>-0.6715418617164137</v>
+        <v>-0.055544666707423</v>
       </c>
       <c r="G49">
-        <v>-3.525788429266316</v>
+        <v>-2.489236757647272</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.068314902390308</v>
       </c>
       <c r="E50">
-        <v>-14.51749273387342</v>
+        <v>-13.79755593613398</v>
       </c>
       <c r="F50">
-        <v>-0.1747989231166482</v>
+        <v>0.04536125172979318</v>
       </c>
       <c r="G50">
-        <v>-4.271952288362648</v>
+        <v>-2.190268011086769</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.014319557678987</v>
       </c>
       <c r="E51">
-        <v>-16.47717174679673</v>
+        <v>-14.74036158216092</v>
       </c>
       <c r="F51">
-        <v>-0.7641988975565525</v>
+        <v>-0.4187788026305894</v>
       </c>
       <c r="G51">
-        <v>-4.238883248970868</v>
+        <v>-3.414428298416312</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.92640987339309</v>
       </c>
       <c r="E52">
-        <v>-15.12647738995092</v>
+        <v>-13.67664568012919</v>
       </c>
       <c r="F52">
-        <v>-0.3959804749707414</v>
+        <v>0.01341526284083024</v>
       </c>
       <c r="G52">
-        <v>-4.932730556910099</v>
+        <v>-2.654105236048516</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.8103012383330364</v>
       </c>
       <c r="E53">
-        <v>-13.33819206126991</v>
+        <v>-12.61817827947235</v>
       </c>
       <c r="F53">
-        <v>-0.0696318827594314</v>
+        <v>-0.1598849963966459</v>
       </c>
       <c r="G53">
-        <v>-4.388539770619162</v>
+        <v>-3.033440786120365</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.6727767250055284</v>
       </c>
       <c r="E54">
-        <v>-14.56790823500081</v>
+        <v>-13.14401109582101</v>
       </c>
       <c r="F54">
-        <v>-0.3817863995237719</v>
+        <v>-0.2005064770951281</v>
       </c>
       <c r="G54">
-        <v>-4.909642812319222</v>
+        <v>-2.592032507187181</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.5199156468984002</v>
       </c>
       <c r="E55">
-        <v>-13.55648715080966</v>
+        <v>-13.56695698271539</v>
       </c>
       <c r="F55">
-        <v>-0.5482749936080278</v>
+        <v>0.1248828656637401</v>
       </c>
       <c r="G55">
-        <v>-4.549753406745051</v>
+        <v>-3.707921402654859</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.3575148599023495</v>
       </c>
       <c r="E56">
-        <v>-13.36403153395768</v>
+        <v>-12.54443660873144</v>
       </c>
       <c r="F56">
-        <v>-0.3146613037727196</v>
+        <v>-0.1921391379594503</v>
       </c>
       <c r="G56">
-        <v>-5.503230248601624</v>
+        <v>-3.690183499655444</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.1915515311189568</v>
       </c>
       <c r="E57">
-        <v>-13.65455125544576</v>
+        <v>-11.8789864102523</v>
       </c>
       <c r="F57">
-        <v>-0.413859956992766</v>
+        <v>0.05845442689844216</v>
       </c>
       <c r="G57">
-        <v>-5.602394329684953</v>
+        <v>-3.772427382487558</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.02582707506182353</v>
       </c>
       <c r="E58">
-        <v>-12.29147605066298</v>
+        <v>-12.61346413803036</v>
       </c>
       <c r="F58">
-        <v>-0.828166256768133</v>
+        <v>-0.08608740121604358</v>
       </c>
       <c r="G58">
-        <v>-4.987516775039498</v>
+        <v>-3.38291190488245</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.13667639973123</v>
       </c>
       <c r="E59">
-        <v>-12.27631019121129</v>
+        <v>-11.10859788359341</v>
       </c>
       <c r="F59">
-        <v>-0.7865258841642075</v>
+        <v>-0.1163286099900451</v>
       </c>
       <c r="G59">
-        <v>-4.589787833951458</v>
+        <v>-3.588354429413002</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.2934502928752146</v>
       </c>
       <c r="E60">
-        <v>-12.20679358671954</v>
+        <v>-12.4053173587418</v>
       </c>
       <c r="F60">
-        <v>-0.4040976471507738</v>
+        <v>-0.2339451840439357</v>
       </c>
       <c r="G60">
-        <v>-5.578541849074504</v>
+        <v>-3.877970884825063</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.445110013240296</v>
       </c>
       <c r="E61">
-        <v>-12.59446266109418</v>
+        <v>-11.88853243346047</v>
       </c>
       <c r="F61">
-        <v>-0.5768230194107071</v>
+        <v>0.05917924837589173</v>
       </c>
       <c r="G61">
-        <v>-4.177472629217388</v>
+        <v>-4.224515481330432</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.5917436740049083</v>
       </c>
       <c r="E62">
-        <v>-13.0305365941368</v>
+        <v>-11.0483148376033</v>
       </c>
       <c r="F62">
-        <v>0.0761541531940592</v>
+        <v>-0.1336265780953044</v>
       </c>
       <c r="G62">
-        <v>-5.502061626026261</v>
+        <v>-3.889537930939277</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.7331275054078812</v>
       </c>
       <c r="E63">
-        <v>-12.94361706403358</v>
+        <v>-10.40017246678148</v>
       </c>
       <c r="F63">
-        <v>-0.359784961305417</v>
+        <v>0.2652290128830463</v>
       </c>
       <c r="G63">
-        <v>-4.562753919077769</v>
+        <v>-4.081129132933518</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.8707175230171489</v>
       </c>
       <c r="E64">
-        <v>-12.10190960022789</v>
+        <v>-10.63175862753374</v>
       </c>
       <c r="F64">
-        <v>-0.2884119975128088</v>
+        <v>-0.1427916350398781</v>
       </c>
       <c r="G64">
-        <v>-4.309394558411806</v>
+        <v>-4.182878750083018</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.004156728670209</v>
       </c>
       <c r="E65">
-        <v>-11.31810320508427</v>
+        <v>-10.88476899881629</v>
       </c>
       <c r="F65">
-        <v>-0.8821020867318117</v>
+        <v>0.08920176815555421</v>
       </c>
       <c r="G65">
-        <v>-5.506971165061</v>
+        <v>-3.706709742987486</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.1343924463408</v>
       </c>
       <c r="E66">
-        <v>-12.59091233747216</v>
+        <v>-11.05276179907884</v>
       </c>
       <c r="F66">
-        <v>-0.8687330652180305</v>
+        <v>0.1331897339790136</v>
       </c>
       <c r="G66">
-        <v>-5.560423233338073</v>
+        <v>-3.777816950625492</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.262976469738882</v>
       </c>
       <c r="E67">
-        <v>-12.17084656004665</v>
+        <v>-10.52537118767154</v>
       </c>
       <c r="F67">
-        <v>-0.5469288965784785</v>
+        <v>-0.3497111853199723</v>
       </c>
       <c r="G67">
-        <v>-4.676299009983692</v>
+        <v>-3.846437938563505</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.388284182292452</v>
       </c>
       <c r="E68">
-        <v>-11.3718471346073</v>
+        <v>-10.24940598164411</v>
       </c>
       <c r="F68">
-        <v>-0.5117796109428899</v>
+        <v>-0.4283845510334525</v>
       </c>
       <c r="G68">
-        <v>-5.172956983421773</v>
+        <v>-4.345492746972019</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.511004318223878</v>
       </c>
       <c r="E69">
-        <v>-12.2348701255671</v>
+        <v>-10.77042955859662</v>
       </c>
       <c r="F69">
-        <v>-0.7063142401837286</v>
+        <v>0.1890059579470471</v>
       </c>
       <c r="G69">
-        <v>-5.13649794539778</v>
+        <v>-3.243494900587122</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.630638676798372</v>
       </c>
       <c r="E70">
-        <v>-11.57173850577988</v>
+        <v>-11.53615828550162</v>
       </c>
       <c r="F70">
-        <v>-0.6707408304379067</v>
+        <v>-0.2645334787597103</v>
       </c>
       <c r="G70">
-        <v>-5.357367612141336</v>
+        <v>-3.999941314128431</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.743970913809414</v>
       </c>
       <c r="E71">
-        <v>-12.40828803769083</v>
+        <v>-10.65726299314494</v>
       </c>
       <c r="F71">
-        <v>-0.7463981104377939</v>
+        <v>-0.4182179978988941</v>
       </c>
       <c r="G71">
-        <v>-5.113913403728872</v>
+        <v>-3.995713747474782</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.850792987310109</v>
       </c>
       <c r="E72">
-        <v>-13.99766920253294</v>
+        <v>-10.39146421126473</v>
       </c>
       <c r="F72">
-        <v>-0.9419458330122564</v>
+        <v>-0.560829729964857</v>
       </c>
       <c r="G72">
-        <v>-4.098724682474744</v>
+        <v>-4.05391313805517</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.948678646644626</v>
       </c>
       <c r="E73">
-        <v>-10.03627788094711</v>
+        <v>-10.85477238698948</v>
       </c>
       <c r="F73">
-        <v>-1.035432064622597</v>
+        <v>-0.7942222457036178</v>
       </c>
       <c r="G73">
-        <v>-4.128923478883976</v>
+        <v>-3.801073533038872</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.033861926697615</v>
       </c>
       <c r="E74">
-        <v>-12.24842384827205</v>
+        <v>-11.82189140996359</v>
       </c>
       <c r="F74">
-        <v>-1.162910352606816</v>
+        <v>-1.069395128137377</v>
       </c>
       <c r="G74">
-        <v>-4.942523150615263</v>
+        <v>-3.925056774030117</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.104958592738366</v>
       </c>
       <c r="E75">
-        <v>-13.08533565810362</v>
+        <v>-11.62720778389984</v>
       </c>
       <c r="F75">
-        <v>-1.31784653489163</v>
+        <v>-0.6051904611195762</v>
       </c>
       <c r="G75">
-        <v>-5.083890066233221</v>
+        <v>-3.336551025150496</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.158182585940229</v>
       </c>
       <c r="E76">
-        <v>-13.11612022440776</v>
+        <v>-11.97698258777829</v>
       </c>
       <c r="F76">
-        <v>-1.10801361645589</v>
+        <v>-1.077740101353179</v>
       </c>
       <c r="G76">
-        <v>-5.699486009260698</v>
+        <v>-3.940162793325812</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.189845675457368</v>
       </c>
       <c r="E77">
-        <v>-14.18607183514806</v>
+        <v>-12.45167534715832</v>
       </c>
       <c r="F77">
-        <v>-1.338775237323359</v>
+        <v>-0.9849447281567731</v>
       </c>
       <c r="G77">
-        <v>-4.010280147847576</v>
+        <v>-3.995763405657871</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.197888789985529</v>
       </c>
       <c r="E78">
-        <v>-13.22001247509174</v>
+        <v>-13.57483652748874</v>
       </c>
       <c r="F78">
-        <v>-0.6800433963713451</v>
+        <v>-1.303894342726278</v>
       </c>
       <c r="G78">
-        <v>-4.486588197855757</v>
+        <v>-3.645203117413367</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.178399743524585</v>
       </c>
       <c r="E79">
-        <v>-14.41653493434642</v>
+        <v>-13.96111988881703</v>
       </c>
       <c r="F79">
-        <v>-1.630797941097464</v>
+        <v>-1.318573013103885</v>
       </c>
       <c r="G79">
-        <v>-3.671425948629934</v>
+        <v>-3.302286878819039</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.129704524623132</v>
       </c>
       <c r="E80">
-        <v>-15.40817564407206</v>
+        <v>-14.28039542025382</v>
       </c>
       <c r="F80">
-        <v>-1.826523762663528</v>
+        <v>-1.20140789928452</v>
       </c>
       <c r="G80">
-        <v>-4.288001813137035</v>
+        <v>-3.910205666740947</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.051819708015422</v>
       </c>
       <c r="E81">
-        <v>-15.71432765783462</v>
+        <v>-14.83185939948589</v>
       </c>
       <c r="F81">
-        <v>-1.324653229840434</v>
+        <v>-1.294598403732062</v>
       </c>
       <c r="G81">
-        <v>-4.18968523171176</v>
+        <v>-2.843670384172723</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.944449503585149</v>
       </c>
       <c r="E82">
-        <v>-15.74388500768269</v>
+        <v>-14.84364248885385</v>
       </c>
       <c r="F82">
-        <v>-1.2252218053802</v>
+        <v>-0.9850051989771775</v>
       </c>
       <c r="G82">
-        <v>-4.47489866155659</v>
+        <v>-2.661560584602955</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.810953375073368</v>
       </c>
       <c r="E83">
-        <v>-17.11603527437684</v>
+        <v>-16.78668388827299</v>
       </c>
       <c r="F83">
-        <v>-1.873049017841762</v>
+        <v>-1.293953933892684</v>
       </c>
       <c r="G83">
-        <v>-4.157589492708525</v>
+        <v>-2.694871293819101</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.655111279459239</v>
       </c>
       <c r="E84">
-        <v>-18.62293028516923</v>
+        <v>-17.4380052478482</v>
       </c>
       <c r="F84">
-        <v>-1.965767352869708</v>
+        <v>-1.643203571321789</v>
       </c>
       <c r="G84">
-        <v>-4.287703864038501</v>
+        <v>-3.1436653998504</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.480273123015313</v>
       </c>
       <c r="E85">
-        <v>-18.53723344304808</v>
+        <v>-18.04503360315439</v>
       </c>
       <c r="F85">
-        <v>-1.861309395009288</v>
+        <v>-1.493598761641393</v>
       </c>
       <c r="G85">
-        <v>-3.428349142408947</v>
+        <v>-1.811001982471244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.293916686982067</v>
       </c>
       <c r="E86">
-        <v>-19.7872688796514</v>
+        <v>-20.11243142729816</v>
       </c>
       <c r="F86">
-        <v>-2.202357366783275</v>
+        <v>-1.751456280254434</v>
       </c>
       <c r="G86">
-        <v>-4.200470989078705</v>
+        <v>-2.275014666346572</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.103415594333854</v>
       </c>
       <c r="E87">
-        <v>-21.84825438460031</v>
+        <v>-20.71052510338722</v>
       </c>
       <c r="F87">
-        <v>-2.572108269064265</v>
+        <v>-1.898040034016821</v>
       </c>
       <c r="G87">
-        <v>-3.095367850977973</v>
+        <v>-2.61901676387778</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.9154739493323811</v>
       </c>
       <c r="E88">
-        <v>-22.9643194461607</v>
+        <v>-22.57398762906956</v>
       </c>
       <c r="F88">
-        <v>-2.183946901256056</v>
+        <v>-1.348565711657047</v>
       </c>
       <c r="G88">
-        <v>-4.077719271028069</v>
+        <v>-2.219238595100931</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.7416473236863959</v>
       </c>
       <c r="E89">
-        <v>-22.66829310027929</v>
+        <v>-23.09145635392605</v>
       </c>
       <c r="F89">
-        <v>-1.941398440614152</v>
+        <v>-1.770207204784204</v>
       </c>
       <c r="G89">
-        <v>-2.98113747714542</v>
+        <v>-2.866228441477317</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.5921550343626337</v>
       </c>
       <c r="E90">
-        <v>-24.60964085041956</v>
+        <v>-25.08900246650151</v>
       </c>
       <c r="F90">
-        <v>-1.982317305210239</v>
+        <v>-2.203413535221844</v>
       </c>
       <c r="G90">
-        <v>-4.157937099990149</v>
+        <v>-2.544354030330597</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4750410954931666</v>
       </c>
       <c r="E91">
-        <v>-24.93914620463968</v>
+        <v>-25.54268763495996</v>
       </c>
       <c r="F91">
-        <v>-1.938789083295334</v>
+        <v>-2.095623055299961</v>
       </c>
       <c r="G91">
-        <v>-3.164766817117714</v>
+        <v>-2.713042878284161</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4015851410937138</v>
       </c>
       <c r="E92">
-        <v>-26.88177098445011</v>
+        <v>-27.17772940322141</v>
       </c>
       <c r="F92">
-        <v>-2.724766440991381</v>
+        <v>-2.057520639873393</v>
       </c>
       <c r="G92">
-        <v>-4.239310309345434</v>
+        <v>-3.017586583532796</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.3790413483092046</v>
       </c>
       <c r="E93">
-        <v>-29.95993779252793</v>
+        <v>-30.20332515654418</v>
       </c>
       <c r="F93">
-        <v>-2.712456073018377</v>
+        <v>-2.431577395914135</v>
       </c>
       <c r="G93">
-        <v>-2.972874355479399</v>
+        <v>-3.601629717025479</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4096927931733066</v>
       </c>
       <c r="E94">
-        <v>-31.58143942350644</v>
+        <v>-31.10814143412076</v>
       </c>
       <c r="F94">
-        <v>-3.053507358261975</v>
+        <v>-2.134703772629237</v>
       </c>
       <c r="G94">
-        <v>-4.298039387212105</v>
+        <v>-2.783812410277161</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4967834251177984</v>
       </c>
       <c r="E95">
-        <v>-32.68088724969569</v>
+        <v>-33.19457696299278</v>
       </c>
       <c r="F95">
-        <v>-3.058271299195475</v>
+        <v>-2.280812043502416</v>
       </c>
       <c r="G95">
-        <v>-4.637323957349852</v>
+        <v>-2.842240228499758</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6393037877922864</v>
       </c>
       <c r="E96">
-        <v>-34.98881723499387</v>
+        <v>-34.9885953397675</v>
       </c>
       <c r="F96">
-        <v>-2.934210855115207</v>
+        <v>-2.718523864243883</v>
       </c>
       <c r="G96">
-        <v>-4.521809091848063</v>
+        <v>-3.609022165214672</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8276371839535019</v>
       </c>
       <c r="E97">
-        <v>-37.32500263386292</v>
+        <v>-37.6217807064296</v>
       </c>
       <c r="F97">
-        <v>-3.214742446277677</v>
+        <v>-2.707996142921704</v>
       </c>
       <c r="G97">
-        <v>-5.177571883903518</v>
+        <v>-2.934839497778713</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.060461706045446</v>
       </c>
       <c r="E98">
-        <v>-39.64702296603597</v>
+        <v>-38.62966731665777</v>
       </c>
       <c r="F98">
-        <v>-3.364769723333501</v>
+        <v>-2.718967869171784</v>
       </c>
       <c r="G98">
-        <v>-5.277454353368868</v>
+        <v>-4.049467075395929</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.320607697579692</v>
       </c>
       <c r="E99">
-        <v>-42.34246579335553</v>
+        <v>-41.37619359502085</v>
       </c>
       <c r="F99">
-        <v>-3.794516791497051</v>
+        <v>-2.869835939141449</v>
       </c>
       <c r="G99">
-        <v>-5.27081339901709</v>
+        <v>-3.94094408207308</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.606652058976535</v>
       </c>
       <c r="E100">
-        <v>-43.20046444240381</v>
+        <v>-44.08306402649877</v>
       </c>
       <c r="F100">
-        <v>-3.546746302747899</v>
+        <v>-3.384096363208216</v>
       </c>
       <c r="G100">
-        <v>-6.110761702695437</v>
+        <v>-4.774042867030674</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.892805061231669</v>
       </c>
       <c r="E101">
-        <v>-45.12923888446178</v>
+        <v>-44.98516095543374</v>
       </c>
       <c r="F101">
-        <v>-3.772059751207156</v>
+        <v>-3.2269401562839</v>
       </c>
       <c r="G101">
-        <v>-5.67526605809539</v>
+        <v>-4.509755395539576</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.198864681611992</v>
       </c>
       <c r="E102">
-        <v>-46.51516024061327</v>
+        <v>-47.0297579129489</v>
       </c>
       <c r="F102">
-        <v>-4.426796376175469</v>
+        <v>-3.452158342491835</v>
       </c>
       <c r="G102">
-        <v>-6.578816562674215</v>
+        <v>-3.933833030254725</v>
       </c>
     </row>
   </sheetData>
